--- a/Project/outputs/tables/table_var_metrics_h1.xlsx
+++ b/Project/outputs/tables/table_var_metrics_h1.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008534537938150037</v>
+        <v>0.0008738736117040344</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01376419029500948</v>
+        <v>0.01376034865375274</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02921393150219607</v>
+        <v>0.02956135334696357</v>
       </c>
       <c r="E2" t="n">
-        <v>8.141291567096909</v>
+        <v>8.094074688354182</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4822934232715008</v>
+        <v>0.4755480607082631</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005808194003051531</v>
+        <v>0.000747002164140833</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01290033408440289</v>
+        <v>0.01501438589782085</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02410019502628875</v>
+        <v>0.02733134032829039</v>
       </c>
       <c r="E3" t="n">
-        <v>8.905376385966756</v>
+        <v>8.628456003559613</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5025295109612141</v>
+        <v>0.4839797639123103</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0005499546506822775</v>
+        <v>0.0008228910429400047</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01295152873268861</v>
+        <v>0.01492166584514395</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02345111192848385</v>
+        <v>0.02868607751052773</v>
       </c>
       <c r="E4" t="n">
-        <v>8.319182576025746</v>
+        <v>8.929827681292918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4789207419898819</v>
+        <v>0.5311973018549747</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000743881069149387</v>
+        <v>0.0005502752076023813</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01539220229630507</v>
+        <v>0.01254562267483908</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0272741831985742</v>
+        <v>0.02345794551111374</v>
       </c>
       <c r="E5" t="n">
-        <v>8.92155219406999</v>
+        <v>8.049036629760927</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4957841483979764</v>
+        <v>0.4873524451939292</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0004899528107345498</v>
+        <v>0.0004993417634426429</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01389766277491357</v>
+        <v>0.01369552090287686</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02213487769865806</v>
+        <v>0.02234595631076556</v>
       </c>
       <c r="E6" t="n">
-        <v>7.764528300946388</v>
+        <v>7.603678062600622</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4890387858347386</v>
+        <v>0.4924114671163575</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003754447764663787</v>
+        <v>0.000535395221996536</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01248043362026348</v>
+        <v>0.01208699207779555</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01937639740680343</v>
+        <v>0.02313860890366005</v>
       </c>
       <c r="E7" t="n">
-        <v>6.708711702620033</v>
+        <v>6.903072242445843</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5193929173693086</v>
+        <v>0.4974704890387858</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0007242391502149965</v>
+        <v>0.0003806843370641</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01532451732917639</v>
+        <v>0.01236453257257241</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02691169170109892</v>
+        <v>0.01951113366937196</v>
       </c>
       <c r="E8" t="n">
-        <v>7.353149350373038</v>
+        <v>6.624699610861227</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5008431703204047</v>
+        <v>0.5261382799325464</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0005400767494338904</v>
+        <v>0.0005094354777850902</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01291557099410416</v>
+        <v>0.01163003788115916</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02323955140345636</v>
+        <v>0.02257067738870702</v>
       </c>
       <c r="E9" t="n">
-        <v>6.895547285418409</v>
+        <v>7.16242047005685</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4755480607082631</v>
+        <v>0.5008431703204047</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0006072278001002045</v>
+        <v>0.0006148623533344528</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01370330501585796</v>
+        <v>0.01325238831324508</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02446274248319495</v>
+        <v>0.024575386621175</v>
       </c>
       <c r="E10" t="n">
-        <v>7.876167420314658</v>
+        <v>7.749408173616523</v>
       </c>
       <c r="F10" t="n">
-        <v>0.493043844856661</v>
+        <v>0.4993676222596964</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0003435699877662086</v>
+        <v>0.0003395299952459204</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01049855026299557</v>
+        <v>0.01036839971579646</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01853564101309174</v>
+        <v>0.01842633971373372</v>
       </c>
       <c r="E11" t="n">
-        <v>6.763106375601871</v>
+        <v>6.666607482533673</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5394088669950738</v>
+        <v>0.5401730531520396</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0002947666859556724</v>
+        <v>0.0004658757976837488</v>
       </c>
       <c r="C12" t="n">
-        <v>0.009670123344005537</v>
+        <v>0.01147068225866826</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01716877065941742</v>
+        <v>0.02158415617261302</v>
       </c>
       <c r="E12" t="n">
-        <v>7.593729371968901</v>
+        <v>7.503824939203094</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5036945812807881</v>
+        <v>0.5006180469715699</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0002793372773533085</v>
+        <v>0.0003943795882572566</v>
       </c>
       <c r="C13" t="n">
-        <v>0.009080890719950633</v>
+        <v>0.01114243328847927</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01671338617256564</v>
+        <v>0.0198589926294678</v>
       </c>
       <c r="E13" t="n">
-        <v>7.989737300955755</v>
+        <v>7.58401061809548</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4950738916256158</v>
+        <v>0.5006180469715699</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0004684642848308186</v>
+        <v>0.0002782018630768031</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01155035419119316</v>
+        <v>0.008903067565216046</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02164403577965114</v>
+        <v>0.01667938437343546</v>
       </c>
       <c r="E14" t="n">
-        <v>7.549504434673929</v>
+        <v>7.835286744128771</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5049261083743842</v>
+        <v>0.4820766378244747</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0009815007199497573</v>
+        <v>0.0009908818376130203</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01404055481895859</v>
+        <v>0.01381251452049463</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03132891188582453</v>
+        <v>0.03147827564548319</v>
       </c>
       <c r="E15" t="n">
-        <v>7.047843147632069</v>
+        <v>6.910633168961636</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5184729064039408</v>
+        <v>0.4969097651421508</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0011944194218389</v>
+        <v>0.0005571459735981893</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01608310966124915</v>
+        <v>0.01217125514101199</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0345603735778261</v>
+        <v>0.02360393978975097</v>
       </c>
       <c r="E16" t="n">
-        <v>6.784134223911413</v>
+        <v>7.115744356978328</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5320197044334976</v>
+        <v>0.4647713226205192</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0003926396148211826</v>
+        <v>0.001178785327716561</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01207660711012286</v>
+        <v>0.01574269721407198</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01981513600309578</v>
+        <v>0.03433344328372208</v>
       </c>
       <c r="E17" t="n">
-        <v>7.316561865531707</v>
+        <v>6.670411175008431</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5320197044334976</v>
+        <v>0.5327564894932015</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0004924152877778752</v>
+        <v>0.0005047785337424968</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01160508838010564</v>
+        <v>0.01115396030099258</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02219043234770056</v>
+        <v>0.02246727695432842</v>
       </c>
       <c r="E18" t="n">
-        <v>7.734733804111539</v>
+        <v>8.285199536018881</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4975369458128079</v>
+        <v>0.484548825710754</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0005558891600367154</v>
+        <v>0.0005886973646167495</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01182565981107264</v>
+        <v>0.0118456262505914</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02274458592989661</v>
+        <v>0.02355397607031683</v>
       </c>
       <c r="E19" t="n">
-        <v>7.347418815548398</v>
+        <v>7.321464752616037</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5153940886699507</v>
+        <v>0.5003090234857849</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
